--- a/output/monthly/2026-05.xlsx
+++ b/output/monthly/2026-05.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,43 +540,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Review of Economic Studies</t>
+          <t>The Quarterly Journal of Economics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quantifying the Benefits of Labour Mobility in a Currency Union</t>
+          <t>Trust and Innovation Within the Firm: Evidence from Matched CEO-Firm Data*</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thu, 24 Jul 2025 00:00:00 GMT</t>
+          <t>Thu, 26 Feb 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Christopher L House; Christian Proebsting; Linda L Tesar</t>
+          <t>Kieu-Trang Nguyen</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/1038/8182042?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/1705/8499649?rss=1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Abstract Unemployment differentials are greater between countries in the euro area than between U.S. states. In both regions, net migration responds to unemployment differentials, though the response is smaller in the euro area compared to the U.S. We use a multi-country DSGE model with cross-border migration to quantify Mundell’s hypothesis that labour mobility could substitute for independent monetary policy in a currency union. While not as effective as independent monetary policy, increased labour mobility reduces business cycle fluctuations for most countries in the euro area. However, Mundell’s conjecture does not hold uniformly. For countries that primarily face demand shocks, labour mobility stabilizes inflation and unemployment and improves welfare. If supply shocks are dominant however, labour mobility increases the cost of being in a currency union by magnifying inflation volatility.</t>
+          <t>Abstract This article shows that a CEO’s trust enhances innovation within a firm, providing a novel micro-foundation for the well-known trust-growth relationship. I build a new matched CEO-firm-patent data set covering 5,753 CEOs in 3,598 U.S. public firms and 700,000 patents during 2000–2011. I exploit variation in generalized trust across CEO ethnic origins, inferred from their last names using deanonymized historical censuses. Following CEO turnovers, a one standard deviation increase in a CEO’s generalized trust is associated with 6% more future patents and 4%–6% higher average patent quality, driven entirely by higher-quality patents. Text analysis of employee reviews shows that the CEO’s trust enhances a firm’s trust culture. These results are consistent with insights from qualitative interviews suggesting that the CEO's trust and the firm’s trust culture encourage researchers to undertake high-risk explorative research and development. In addition, changes in the CEO’s bilateral trust toward inventors in different countries have comparable effects on inventors’ patenting, controlling for CEO and other fixed effects.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf055</t>
+          <t>10.1093/qje/qjag013</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>monetary policy</t>
+          <t>patent</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>high-value keyword override: monetary policy</t>
+          <t>high-value keyword override: patent</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -598,43 +598,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Review of Economic Studies</t>
+          <t>The Quarterly Journal of Economics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Demand Shocks as Technology Shocks</t>
+          <t>Monetary Policy and Sovereign Risk in Emerging Economies (NK-Default)*</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thu, 19 Jun 2025 00:00:00 GMT</t>
+          <t>Mon, 23 Feb 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Yan Bai; José-Víctor Ríos-Rull; Kjetil Storesletten</t>
+          <t>Cristina Arellano; Yan Bai; Gabriel Mihalache</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/798/8169445?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/1635/8494845?rss=1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Abstract We provide a macroeconomic theory where demand for goods has a productive role. A search friction prevents perfect matching between producers and potential customers. Larger demand induces more search, which, in turn, increases GDP and measured total factor productivity (TFP). We embed the product-market friction in a standard neoclassical model and estimate it using Bayesian techniques. Business cycles are driven by preference shocks, true technology shocks, and investment-specific shocks. Preference shocks have qualitatively similar effects as true productivity shocks. These shocks account for a large share of the fluctuations in consumption, GDP, and measured TFP and can be identified using shopping time data.</t>
+          <t>Abstract This article develops a New Keynesian model with sovereign default risk. Inflation is set by forward-looking firms, monetary policy is an interest rate rule, and the fiscal government borrows externally, long-term, with an option to default. In this framework, default risk creates inflation pressures through an expectations channel, and tight monetary policy disincentivizes fiscal overborrowing. The model sheds light on temporary inflation events in emerging-market data: short-lived spikes in inflation, spreads, and domestic policy rates. As spreads rise, firms increase their prices in expectation of higher future inflation and low consumption during default. Monetary policy tightens, which reduces inflation and helps bring spreads down by disciplining government borrowing. These monetary-fiscal interactions imply that delivering the flexible-prices allocation may not be optimal for monetary policy.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf045</t>
+          <t>10.1093/qje/qjag012</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>total factor productivity; tfp</t>
+          <t>monetary policy</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>high-value keyword override: total factor productivity, tfp</t>
+          <t>high-value keyword override: monetary policy</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -661,38 +661,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trust and Innovation Within the Firm: Evidence from Matched CEO-Firm Data*</t>
+          <t>Automation and Rent Dissipation: Implications for Wages, Inequality, and Productivity*</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 00:00:00 GMT</t>
+          <t>Fri, 30 Jan 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kieu-Trang Nguyen</t>
+          <t>Daron Acemoglu; Pascual Restrepo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/1705/8499649?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/1521/8445541?rss=1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Abstract This article shows that a CEO’s trust enhances innovation within a firm, providing a novel micro-foundation for the well-known trust-growth relationship. I build a new matched CEO-firm-patent data set covering 5,753 CEOs in 3,598 U.S. public firms and 700,000 patents during 2000–2011. I exploit variation in generalized trust across CEO ethnic origins, inferred from their last names using deanonymized historical censuses. Following CEO turnovers, a one standard deviation increase in a CEO’s generalized trust is associated with 6% more future patents and 4%–6% higher average patent quality, driven entirely by higher-quality patents. Text analysis of employee reviews shows that the CEO’s trust enhances a firm’s trust culture. These results are consistent with insights from qualitative interviews suggesting that the CEO's trust and the firm’s trust culture encourage researchers to undertake high-risk explorative research and development. In addition, changes in the CEO’s bilateral trust toward inventors in different countries have comparable effects on inventors’ patenting, controlling for CEO and other fixed effects.</t>
+          <t>Abstract This article studies the effects of automation in a task-based economy in which some jobs pay workers rents—wages above workers' outside options. We show that automation targets high-rent tasks, dissipating rents, amplifying wage losses, and reducing within-group wage dispersion in exposed groups. This form of rent dissipation is inefficient and offsets the productivity gains from automation. Using U.S. data from 1980 to 2016, we find evidence of sizable rent dissipation and reduced within-group wage dispersion due to automation. Automation accounts for 52% of the increase in between-group inequality since 1980, with rent dissipation explaining one-fifth of this total. Our estimates imply that inefficient rent dissipation has offset 60%–90% of the productivity gains from automation over this period.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjag013</t>
+          <t>10.1093/qje/qjag006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>patent</t>
+          <t>automation</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -702,126 +702,10 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>high-value keyword override: patent</t>
+          <t>high-value keyword override: automation</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
-        <is>
-          <t>rss+crossref</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>The Quarterly Journal of Economics</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Monetary Policy and Sovereign Risk in Emerging Economies (NK-Default)*</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Mon, 23 Feb 2026 00:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Cristina Arellano; Yan Bai; Gabriel Mihalache</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://academic.oup.com/qje/article/141/2/1635/8494845?rss=1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Abstract This article develops a New Keynesian model with sovereign default risk. Inflation is set by forward-looking firms, monetary policy is an interest rate rule, and the fiscal government borrows externally, long-term, with an option to default. In this framework, default risk creates inflation pressures through an expectations channel, and tight monetary policy disincentivizes fiscal overborrowing. The model sheds light on temporary inflation events in emerging-market data: short-lived spikes in inflation, spreads, and domestic policy rates. As spreads rise, firms increase their prices in expectation of higher future inflation and low consumption during default. Monetary policy tightens, which reduces inflation and helps bring spreads down by disciplining government borrowing. These monetary-fiscal interactions imply that delivering the flexible-prices allocation may not be optimal for monetary policy.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>10.1093/qje/qjag012</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>monetary policy</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>selected</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>high-value keyword override: monetary policy</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>rss+crossref</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>The Quarterly Journal of Economics</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Automation and Rent Dissipation: Implications for Wages, Inequality, and Productivity*</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Fri, 30 Jan 2026 00:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Daron Acemoglu; Pascual Restrepo</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://academic.oup.com/qje/article/141/2/1521/8445541?rss=1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Abstract This article studies the effects of automation in a task-based economy in which some jobs pay workers rents—wages above workers' outside options. We show that automation targets high-rent tasks, dissipating rents, amplifying wage losses, and reducing within-group wage dispersion in exposed groups. This form of rent dissipation is inefficient and offsets the productivity gains from automation. Using U.S. data from 1980 to 2016, we find evidence of sizable rent dissipation and reduced within-group wage dispersion due to automation. Automation accounts for 52% of the increase in between-group inequality since 1980, with rent dissipation explaining one-fifth of this total. Our estimates imply that inefficient rent dissipation has offset 60%–90% of the productivity gains from automation over this period.</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>10.1093/qje/qjag006</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>automation</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>selected</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>high-value keyword override: automation</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
         <is>
           <t>rss+crossref</t>
         </is>
@@ -838,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3596,44 +3480,44 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Auctions with Frictions: Recruitment, Entry, and Limited Commitment</t>
+          <t>Correction to: Tax Policy and Lumpy Investment Behaviour: Evidence from China's VAT Reform</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tue, 14 Oct 2025 00:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Stephan Lauermann; Asher Wolinsky</t>
-        </is>
-      </c>
+          <t>Wed, 28 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/1167/8286073?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/2133/8443174?rss=1</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Abstract Auction models are convenient abstractions of informal price-formation processes that arise in markets for assets or services. These processes involve frictions like bidder recruitment costs for sellers, participation costs for bidders, and limitations on sellers’ commitment abilities. This paper develops an auction model that captures such frictions. We derive novel insights, notably that outcomes are often inefficient, that markets sometimes unravel, and that the observability of competition may have a large effect.</t>
+          <t>This is a correction to: Zhao Chen, Xian Jiang, Zhikuo Liu, Juan Carlos Suárez Serrato, Daniel Yi Xu, Tax Policy and Lumpy Investment Behaviour: Evidence from China's VAT Reform, The Review of Economic Studies, Volume 90, Issue 2, March 2023, Pages 634–674, https://doi.org/10.1093/restud/rdac027</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf052</t>
+          <t>10.1093/restud/rdag006</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>review</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>no priority JEL or keyword signal</t>
+          <t>weak keyword signal only: policy</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3650,32 +3534,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Search Direction: Position Externalities and Position Auction Bias</t>
+          <t>The Effect of Provider Diversity on Racial Health Disparities: Evidence from the Military*</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fri, 29 Aug 2025 00:00:00 GMT</t>
+          <t>Wed, 01 Oct 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Simon P Anderson; Régis Renault</t>
+          <t>Michael Frakes; Jonathan Gruber</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/763/8244205?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1815/8270662?rss=1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Abstract We formulate a tractable model of pricing under directed search with heterogeneous firm demands. Demand characteristics drive bids in a position auction and enable us to bridge insights from the ordered search literature to those in the position auction literature. Equilibrium pricing implies that the marginal consumer’s surplus decreases down the search order, so consumers optimally follow the firms’ position ordering. A firm suffers from “business stealing” by firms that precede it and “search appeal” from subsequent firms. We find rankings that achieve the maximal joint profit or consumer surplus by constructing firm-specific scores. A generalized second price auction for positions endogenizes equilibrium orders and bids are driven by position externalities that impact incremental profit from switching positions. The joint profit maximization order is upheld when firm heterogeneity concerns mostly their mark-up potentials. But the consumer welfare order is robust when firms differ mostly over their potential market sizes.</t>
+          <t>Abstract We assess the relationship between the racial diversity of medical providers and racial health disparities in the use of preventive care and in patient outcomes. We use unique data from the Military Health System, where we observe providers as patients so that we can identify their race, and where moves across bases change exposure to provider race in a plausibly exogenous fashion. We consider patients with four chronic, deadly, but manageable illnesses, where the relationship with the provider may have the most direct impact on health. We find striking evidence that provider racial diversity leads to reduced disparities in maintenance of preventive care and mortality.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf051</t>
+          <t>10.1093/restud/rdaf072</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -3704,38 +3588,38 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bargaining Foundations for the Outside Option Principle</t>
+          <t>The Impact of EITC on Education, Labour Market Trajectories, and Inequalities</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mon, 07 Jul 2025 00:00:00 GMT</t>
+          <t>Mon, 29 Sep 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Dilip Abreu; Mihai Manea</t>
+          <t>Julien Albertini; Arthur Poirier; Anthony Terriau</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/725/8189048?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1393/8267991?rss=1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Abstract We study a bargaining game in which a seller can trade with one of two buyers, who have values h and l (h&gt;l). The outside option principle (OOP) predicts that, as players become patient, the seller trades with the high-value buyer with probability converging to 1 at a price converging to max(h/2,l). While this prediction is supported by the Markov perfect equilibrium (MPE), a wide range of trading outcomes may emerge in subgame perfect equilibria (SPEs): in the patient limit, the seller can obtain any price in the interval [h/2,h] (and no other); moreover, allocative inefficiency and costly delay are possible. We propose equilibrium refinements less restrictive than Markov behavior that guarantee trading outcomes consistent with the OOP. One refinement requires that a buyer’s relative probability of trade does not increase dramatically following a failed negotiation with that buyer. Another refinement posits that the seller does not approach a buyer hoping that negotiations fail. SPEs satisfying both refinements conform with the OOP (but need not be MPEs). Our benchmark model features strategic matching by the seller. We provide a parallel analysis for the random matching protocol. Under random matching, prices in SPEs may also rise above and fall below l , but have a narrower range. A refinement particular to this protocol that restores the OOP requires that a random mismatch should not impact the seller excessively.</t>
+          <t>Abstract As a complement to the federal earned income tax credit (EITC), some states offer their own EITC, typically calculated as a percentage of the federal EITC. In this paper, we analyse the effect of state EITC on education using policy discontinuities at US state borders. Our estimates reveal that an increase in the state EITC leads to a statistically significant increase in the high school dropout rate. We then use a life-cycle matching model with directed search and endogenous educational choices, search intensities, hirings, hours worked, and separations to investigate the effects of EITC on the labour market in the long run and along the transitional dynamics. We show that a tax credit targeted at low-wage (and low-skilled) workers reduces the relative return to schooling, thereby generating a powerful disincentive to pursue long-term studies. In the long run, this results in an increase in the proportion of low-skilled workers in the economy, which may have important implications for employment, productivity, and income inequality. Finally, we use the model to determine the optimal design of the EITC.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf053</t>
+          <t>10.1093/restud/rdaf073</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>trade</t>
+          <t>productivity; policy</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3745,7 +3629,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>weak keyword signal only: trade</t>
+          <t>weak keyword signal only: productivity, policy</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3762,32 +3646,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Endogenous Clustering and Analogy-Based Expectation Equilibrium</t>
+          <t>Religion, Education, and the State</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wed, 02 Jul 2025 00:00:00 GMT</t>
+          <t>Fri, 26 Sep 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Philippe Jehiel; Giacomo Weber</t>
+          <t>Samuel Bazzi; Masyhur Hilmy; Benjamin Marx</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/1077/8181852?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1494/8266500?rss=1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Abstract Normal-form two-player games are categorized by players into K analogy classes so as to minimize the prediction error about the behaviour of the opponent. This results in Clustered Analogy-Based Expectation Equilibria in which strategies are analogy-based expectation equilibria given the analogy partitions and analogy partitions minimize the prediction errors given the strategies. We distinguish between environments with self-repelling analogy partitions in which some mixing over partitions is required and environments with self-attractive partitions in which several analogy partitions can arise, thereby suggesting new channels of belief heterogeneity and equilibrium multiplicity. Various economic applications are discussed.</t>
+          <t>Abstract This paper explores how state and religious providers of education compete during the nation building process. Using novel administrative data, we characterize the evolution of Indonesia’s Islamic education system and religious school choice after the introduction of mass public primary schooling in the 1970s. Funded through informal taxation, Islamic schools competed with the state by entering in the same markets. While primary enrollment shifted towards state schools, religious education increased overall as Islamic schools absorbed growing demand for secondary education. In the short run, electoral support for the secular regime weakened in markets with greater public school construction. Over the long run, Islamic schools established at this juncture are more differentiated in terms of religious curriculum, and cohorts exposed to mass public schooling as children are more invested in religion than in the national identity. Our findings offer a new perspective on the political economy of education reforms and the emergence of parallel systems of public goods provision.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf054</t>
+          <t>10.1093/restud/rdaf071</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -3816,32 +3700,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Behavioural Causal Inference</t>
+          <t>Homeownership, Polarization, and Inequality</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tue, 24 Jun 2025 00:00:00 GMT</t>
+          <t>Fri, 26 Sep 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ran Spiegler</t>
+          <t>Andrii Parkhomenko</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/1323/8172453?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/2021/8266405?rss=1</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Abstract When inferring causal effects from correlational data, a common practice by professional researchers but also lay people is to control for potential confounders. Inappropriate controls produce erroneous causal inferences. I model decision-makers (DMs) who use endogenous observational data to learn actions’ causal effect on payoff-relevant outcomes. Different DM types use different controls. Their resulting choices affect the very correlations they learn from, thus calling for an equilibrium analysis of the steady-state welfare cost of bad controls. I obtain tight upper bounds on this cost. Equilibrium forces drastically reduce it when types’ sets of controls contain one another.</t>
+          <t>Abstract Why are job polarization and income inequality higher in large U.S. cities? I offer a new explanation: when house prices grow faster in large cities, middle-income households increasingly cannot afford to own a house there. They move to smaller cities and the middle of the income distribution in large cities hollows out, making them more polarized and unequal. I document that (1) cities with higher price growth experienced larger polarization and increase in inequality since 1980 and (2) middle-income households migrate more often to cheaper locations for housing-related reasons than low- or high-income households. Using a spatial equilibrium model with tenure choice and skill heterogeneity, I find that excess growth of prices relative to incomes and rents in large cities accounts for nearly all of the gap in polarization and almost one-half of the gap in inequality growth between large and small cities from 1980 to 2019.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf050</t>
+          <t>10.1093/restud/rdaf068</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -3870,38 +3754,38 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Good Dispersion, Bad Dispersion</t>
+          <t>Policy Diffusion and Polarization across U.S. States</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tue, 24 Jun 2025 00:00:00 GMT</t>
+          <t>Thu, 25 Sep 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Matthias Kehrig; Nicolas Vincent</t>
+          <t>Stefano DellaVigna; Woojin Kim</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/1103/8172429?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1602/8263742?rss=1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Abstract We document that most dispersion in marginal revenue products of inputs occurs across plants within firms rather than between firms. This is commonly thought to reflect misallocation: dispersion is “bad”. However, we show that eliminating frictions hampering internal capital markets in a multi-plant firm model may in fact increase productivity dispersion and raise output: dispersion can be “good”. This arises as firms optimally stagger investment activity across their plants over time to avoid raising costly external finance, instead relying on reallocating internal funds. The staggering in turn generates dispersion in marginal revenue products. We use U.S. Census data on multi-plant manufacturing firms to provide empirical evidence for the model mechanism and show a quantitatively important role for good dispersion. Since there is less scope for good dispersion in emerging economies, the difference in the degree of misallocation between emerging and developed economies looks more pronounced than previously thought.</t>
+          <t>Abstract Economists have studied the impact of numerous state laws, from welfare rules to voting ID requirements. Yet for all this policy evaluation, what do we know about policy diffusion—how these policies are introduced and spread from state to state? We present a series of facts based on a data set of 602 U.S. state policies spanning the past seven decades. First, proxies of state capacity do not predict a higher likelihood of innovating new policies, but the political leaning of the state does predict a higher likelihood of introducing partisan laws since 1990. Second, the diffusion of policies from 1950 to 2000 is best predicted by proximity—a state is more likely to adopt a policy if nearby states have already done so—as well as similarity in voter policy preferences. Third, since 2000, party alignment has become the strongest predictor of diffusion, and the speed of adoption has increased. Models of learning and correlated preferences can account for the earlier patterns, but the findings for the last two decades indicate a sharply increasing role of party control. We conclude that party polarization has emerged as a key factor recently for policy adoption, plausibly leading to a worse match between state policies and voter preferences.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf042</t>
+          <t>10.1093/restud/rdaf070</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>productivity</t>
+          <t>policy</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3911,7 +3795,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>weak keyword signal only: productivity</t>
+          <t>weak keyword signal only: policy</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3928,32 +3812,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Overconfidence and Prejudice</t>
+          <t>The Value of Information in a Congested Fishery</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wed, 18 Jun 2025 00:00:00 GMT</t>
+          <t>Wed, 24 Sep 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Paul Heidhues; Botond Kőszegi; Philipp Strack</t>
+          <t>Gabriel Englander; Larry Karp; Leo Simon</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/968/8166803?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1789/8262989?rss=1</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Abstract We develop a model of multi-dimensional misspecified learning in which an overconfident agent learns about groups in society from observations of his and others’ successes. We show that the average person sees his group relative to other groups too positively, and this in-group bias exhibits systematic comparative-statics patterns. First, a person is most likely to have negative opinions about other groups he competes with. Second, while information about another group’s achievements does not lower a person’s prejudice, information about economic or social forces affecting the group can, and personal contact with group members has a beneficial effect that is larger than in classical settings. Third, the agent’s beliefs are subject to “bias substitution”, whereby forces that decrease his bias regarding one group tend to increase his biases regarding unrelated other groups.</t>
+          <t>Abstract We model a fishery with potential congestion, in which firms obtain public and private signals about the location of the densest fish stock. We analytically determine the regions of parameter space where greater precision of public and/or private information increases welfare, and we examine the effects of two types of information sharing. Using high-resolution data from the world’s largest fishery, we estimate the structural model. Point estimates imply that more precise private information raises welfare, whereas more precise public information has a negligible effect on welfare. Moreover, welfare is much more sensitive to changes in the precision of private information than to changes in the precision of public information. This difference reflects the fact that public information increases congestion more than private information does. We also find empirically that a small amount of information sharing can reduce welfare, whereas more extensive information sharing raises welfare, as do information clubs.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf048</t>
+          <t>10.1093/restud/rdaf069</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -3982,32 +3866,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Revisiting the Non-Parametric Analysis of Time-Inconsistent Preferences</t>
+          <t>A Walrasian Mechanism with Markups for Nonconvex Markets</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tue, 17 Jun 2025 00:00:00 GMT</t>
+          <t>Tue, 16 Sep 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Federico Echenique; Gerelt Tserenjigmid</t>
+          <t>Paul Milgrom; Mitchell Watt</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/926/8165928?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1995/8255713?rss=1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Abstract We revisit the recent revealed preference analysis of sophisticated quasi-hyperbolic consumers by Blow et al. [(2021), “Non-parametric Analysis of Time-Inconsistent Preferences”, The Review of Economic Studies , 88 , 2687–2734] (BBC). We show that BBC’s revealed preference test is too lax. There are non-rationalizable data that would pass their test. A basic problem with their test is that it requires finding a certain endogenous elasticity, without regard to the rationalizing utility. Their approach motivates a more stringent test, also based on first-order conditions, that would connect the endogenous elasticity and utility: We show that this test is also too lax. Aside from testing, we also discuss the possibility of recovering model parameters. We show that, even when discount factors are exactly identified, the approach followed in BBC allows for incorrect parameter values to lie in their identified set.</t>
+          <t>Abstract We introduce markup equilibrium —an extension of Walrasian equilibrium in which consumers pay a fixed percentage markup over producer prices. In quasilinear markets, markup equilibria exist despite nonconvexities. They are resource-feasible and envy-free, incur no budget deficit, and require little more communication and computation than ordinary Walrasian equilibrium. The associated markup mechanism is asymptotically incentive-compatible. We also introduce a Bound-Form First Welfare Theorem, which states that for any feasible allocation, the welfare loss compared to the first-best is bounded, using any price vector, by the sum of the resulting (i) budget surplus and (ii) rationing losses suffered by the participants. Using producer prices, this bound implies that any markup equilibrium with a small markup and few unallocated goods is nearly efficient.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf047</t>
+          <t>10.1093/restud/rdaf067</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -4036,44 +3920,48 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Making Decisions Under Model Misspecification</t>
+          <t>Globalization and the Ladder of Development: Pushed to the Top or Held at the Bottom?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tue, 17 Jun 2025 00:00:00 GMT</t>
+          <t>Sat, 30 Aug 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Simone Cerreia-Vioglio; Lars Peter Hansen; Fabio Maccheroni; Massimo Marinacci</t>
+          <t>David Atkin; Arnaud Costinot; Masao Fukui</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/892/8164809?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1455/8244483?rss=1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Abstract We use decision theory to confront uncertainty that is sufficiently broad to incorporate “models as approximations.” We presume the existence of a featured collection of what we call “structured models” that have explicit substantive motivations. The decision-maker confronts uncertainty through the lens of these models, but also views these models as simplifications, and hence, as misspecified. We extend the max–min analysis under model ambiguity to incorporate the uncertainty induced by acknowledging that the models used in decision making are simplified approximations. Formally, we provide an axiomatic rationale for a decision criterion that incorporates model misspecification concerns. We then extend our analysis beyond the max-min case allowing for a more general criterion that encompasses a Bayesian formulation.</t>
+          <t>Abstract We study the relationship between international trade and development in a model where countries differ in their capability, goods differ in their complexity, and capability growth is a function of a country’s pattern of specialization. Theoretically, we show that it is possible for international trade to increase capability growth in all countries and, in turn, to push all countries up the development ladder. This occurs if (i) shifting employment towards more complex sectors raises capability growth and if (ii) foreign competition is tougher in less complex sectors for all countries. Empirically, we provide causal evidence consistent with (i) using the entry of countries into the World Trade Organization as an instrumental variable for other countries’ patterns of specialization. The opposite of (ii), however, holds in the data. Through the lens of our model, these two empirical observations imply dynamic welfare losses from trade that are pervasive, albeit small for the median country. The same economic forces also suggest that the emergence of China has held back capability growth for a number of African countries who are pushed away from their most-complex sectors, which China exports, and into their least-complex sectors, which China imports.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf046</t>
+          <t>10.1093/restud/rdaf077</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>trade; development</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>review</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>no priority JEL or keyword signal</t>
+          <t>weak keyword signal only: trade, development</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4090,32 +3978,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pseudo Lindahl Equilibrium as a Collective Choice Rule</t>
+          <t>A Dynamic Theory of Random Price Discounts</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tue, 17 Jun 2025 00:00:00 GMT</t>
+          <t>Fri, 29 Aug 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Faruk Gul; Wolfgang Pesendorfer</t>
+          <t>Francesc Dilmé; Daniel F Garrett</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/938/8164523?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1671/8243883?rss=1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Abstract A collective choice problem specifies a finite set of alternatives from which a group of expected utility maximizers must choose. We associate a collective pseudo market with every collective choice problem and establish the existence and efficiency of pseudo Lindahl equilibrium (PLE) allocations. We also associate a cooperative bargaining problem with every collective choice problem and define a set-valued solution concept, the ω - weighted Nash bargaining set where ω is a vector of welfare weights. We provide axioms that characterize the ω -weighted Nash bargaining set. Our main result shows that ω -weighted Nash bargaining set payoffs are also the PLE payoffs of the corresponding collective pseudo market with the same utility functions and incomes ω . We define a pseudo core for collective pseudo markets and show that pseudo Lindahl equilibria are in the pseudo core. We characterize the set of PLE outcomes of discrete allocation problems and show that they contain the set of pseudo Walrasian equilibrium outcomes.</t>
+          <t>Abstract A seller with commitment power sets prices over time. Risk-averse buyers arrive to the market and decide when to purchase. We show that it is optimal for the seller to choose a constant high price punctuated by occasional episodes of sequential discounts that occur at random times. This optimal price-path has the property that the price a buyer ends up paying is independent of his arrival and purchase times, and only depends on his valuation. Our theory accommodates empirical findings on the timing of discounts.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf043</t>
+          <t>10.1093/restud/rdaf074</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -4144,32 +4032,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Community Enforcement with Endogenous Records</t>
+          <t>Brokering Votes With Information Spread Via Social Networks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sat, 14 Jun 2025 00:00:00 GMT</t>
+          <t>Fri, 29 Aug 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Harry Pei</t>
+          <t>Raul Duarte; Frederico Finan; Horacio Larreguy; Laura Schechter</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/1241/8161414?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1710/8243643?rss=1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Abstract I study repeated games with anonymous random matching where players can add or remove signals from their records. The ability to manipulate records introduces monotonicity constraints on players’ continuation values, under which sufficiently long-lived players will almost never cooperate. When players’ expected lifespans are intermediate, their ability to sustain cooperation depends on (i) whether their actions are complements or substitutes and (ii) whether manipulation takes the form of adding or removing signals.</t>
+          <t>Abstract Politicians rely on political brokers to buy votes throughout much of the developing world. We investigate how social networks facilitate these vote-buying exchanges. Our conceptual framework suggests brokers should be particularly well-placed within the network to learn about non-copartisans’ reciprocity in order to target transfers effectively. As a result, parties should recruit brokers who are central among non-copartisans. We combine village network data from brokers and citizens with broker reports of vote buying, allowing us to use broker and citizen fixed effects. We show that networks diffuse information about citizens to brokers who leverage it to target transfers. In particular, among those citizens who are not registered to their party, brokers target reciprocal citizens about whom they can learn more through their network, and these citizens are more likely to support the brokers’ party. Moreover, recruited brokers are significantly more central than other citizens among non-copartisans, but not among copartisans. These results highlight the importance of information diffusion through social networks for vote buying, broker recruitment, and ultimately for political outcomes.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf049</t>
+          <t>10.1093/restud/rdaf075</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -4198,32 +4086,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hiring as Exploration</t>
+          <t>Bewley Banks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thu, 12 Jun 2025 00:00:00 GMT</t>
+          <t>Thu, 28 Aug 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Danielle Li; Lindsey Raymond; Peter Bergman</t>
+          <t>Rustam Jamilov; Tommaso Monacelli</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/1200/8160842?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1889/8242670?rss=1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Abstract This article views hiring as a contextual bandit problem: to find the best workers over time, firms must balance “exploitation” (selecting from groups with proven track records) with “exploration” (selecting from under-represented groups to learn about quality). Yet modern hiring algorithms, based on supervised learning approaches, are designed solely for exploitation. Instead, we build a resume screening algorithm that values exploration by evaluating candidates according to their statistical upside potential. Using data from professional services recruiting within a Fortune 500 firm, we show that this approach improves the quality (as measured by eventual hiring rates) of candidates selected for an interview, while also increasing demographic diversity, relative to the firm’s existing practices. The same is not true for traditional supervised learning-based algorithms, which improve hiring rates but select far fewer Black and Hispanic applicants. Together, our results highlight the importance of incorporating exploration in developing decision-making algorithms that are potentially both more efficient and equitable.</t>
+          <t>Abstract How do movements in the distributions of bank size and income affect the macroeconomy? To answer this question, we develop a dynamic general equilibrium model with heterogeneous financial intermediaries, incomplete markets, and aggregate uncertainty. We find that market incompleteness and uninsured idiosyncratic bank rate of return risk generate minimal concentration in the bank net worth distribution, leading to an “as-if” result, whereby the economy behaves as if it had a representative bank. However, introducing ex ante heterogeneity in the banks’ rates of return significantly raises concentration and amplifies real and financial fluctuations relative to the representative-bank case, as this increases a key sufficient statistic, the average marginal propensity to lend. We then extend the model with two empirically validated features of the banking sector—countercyclical return risk and deposit market power—and show that these amplify and dampen aggregate fluctuations, respectively. Finally, because in the model with ex ante heterogeneity the distribution of bank size is highly concentrated, shocks to the largest banks can account for almost all of the aggregate variation that is due to idiosyncratic risk, leading to granular banking and economic cycles. The failure of granular banks (“too big to fail”) produces sizeable macroeconomic crises.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf040</t>
+          <t>10.1093/restud/rdaf062</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -4252,32 +4140,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Surviving Childhood: Effects of Removing a Child From Home</t>
+          <t>A Tale of Two Networks: Common Ownership and Product Market Rivalry</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wed, 11 Jun 2025 00:00:00 GMT</t>
+          <t>Wed, 06 Aug 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ronja Helénsdotter</t>
+          <t>Florian Ederer; Bruno Pellegrino</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/1001/8160240?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1746/8223139?rss=1</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Abstract This paper studies the effects of the court-ordered removal of children from home on health, crime, and education. To isolate causal effects, I exploit quasi-random variation in judge assignment together with across-judge variation in the tendency to favour removal in an instrumental variable design. Using a novel data set (N=26,579) based on Swedish court documents that I transcribe and link with detailed register data, I find that court-ordered out-of-home placement has large adverse effects on the mortality of the marginal child. These effects are primarily driven by suicides that occur while the removed child is still placed in out-of-home care. Removal also causes an increase in hospitalizations for mental illness and non-narcotic crimes. There is little evidence of adverse health effects for birth parents. I explore potential explanations for the detrimental effects on child health. Adverse care conditions and peer exposure appear to be important channels.</t>
+          <t>Abstract We study the welfare implications of the rise of common ownership in the U.S. from 1995 to 2021. We build a general equilibrium model with a hedonic demand system in which firms compete in a network game of oligopoly. Firms are connected through two large networks: the first reflects ownership overlap, the second product market rivalry. In our model, common ownership of competing firms induces unilateral incentives to soften competition and the magnitude of the common ownership effect depends on how much the two networks overlap. We estimate our model for the universe of U.S. public corporations using a combination of firm financials, investor holdings, and text-based product similarity data. We perform counterfactual calculations to evaluate how the efficiency and the distributional impact of common ownership have evolved over time. Under the assumption that firms maximise a share-weighted average of their shareholders’ income, we find that the welfare cost of common ownership, measured as the ratio of deadweight loss to total surplus, has increased about ninefold between 1995 and 2021. Under alternative assumptions about corporate governance, the deadweight loss of common ownership ranges between 3.5 and 13.2% of total surplus in 2021. The rise of common ownership has also led to a significant reallocation of surplus from consumers to producers.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf044</t>
+          <t>10.1093/restud/rdaf057</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -4306,32 +4194,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Complexity and Satisficing: Theory with Evidence from Chess</t>
+          <t>The Geography of Business Dynamism and Skill-Biased Technical Change</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fri, 06 Jun 2025 00:00:00 GMT</t>
+          <t>Tue, 05 Aug 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Yuval Salant; Jörg L Spenkuch</t>
+          <t>Hannah Rubinton</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/1296/8158031?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/2099/8222576?rss=1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Abstract We develop a satisficing model of choice in which the available alternatives differ in their inherent complexity. We assume—and experimentally validate—that complexity leads to errors in the perception of alternatives’ values. The model yields sharp predictions about the effect of complexity on choice probabilities, some of which qualitatively contrast with those of maximization-based choice models. We confirm the predictions of the satisficing model—and thus reject maximization—in a novel data set with information on hundreds of millions of real-world chess moves by highly experienced players. Looking beyond chess, our work offers a blueprint for incorporating complexity at the level of individual objects into models of choice and for detecting satisficing outside of the laboratory.</t>
+          <t>Abstract This paper shows that the growing disparities between big and small cities in the U.S. since 1980 can be explained by firms endogenously responding to a skill-biased technology shock. With the introduction of a new skill-biased technology that is high fixed cost but low marginal cost, firms endogenously adopt more in big cities, cities that offer abundant amenities for high-skilled workers, and cities that are more productive in using high-skilled labour. In cities with more adoption, small and unproductive firms are more likely to exit the market, increasing the equilibrium rate of turnover or business dynamism—a selection effect similar to Melitz (2003). Differences in technology adoption and selection account for three key components of the growing regional disparities, known as the Great Divergence: (1) big cities saw a larger increase in the relative wages and supply of skilled workers, (2) big cities saw a smaller decline in business dynamism, and (3) firms in big cities invest more intensively in information and communication technology.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf041</t>
+          <t>10.1093/restud/rdaf063</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -4360,32 +4248,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Public Listing Choice with Persistent Hidden Information</t>
+          <t>Women in the Courtroom: Technology and Justice</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fri, 06 Jun 2025 00:00:00 GMT</t>
+          <t>Fri, 01 Aug 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Francesco Celentano; Mark Rempel</t>
+          <t>Heng Chen; Yuyu Chen; Qingxu Yang</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/833/8157751?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1574/8220859?rss=1</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Abstract How much does firm intangibility amplify CEOs’ persistent private information and reduce firms’ public listing propensity? We develop a model of competing public and private investors financing firms heterogeneously exposed to persistent private cash flows. Equilibrium financing is driven by information rent differentials in CEO compensation. We validate and structurally estimate the model using firm listing and CEO compensation data. We find private (intangible) cash flows exhibit 63% higher persistence than their tangible counterparts. Further, if firm intangibility levels returned to those of 1980, mean listing propensities would increase 5 percentage points while mean CEO variable pay growth would decrease by 61%.</t>
+          <t>Abstract Our study analyses 6 million civil judgments in China from 2014 to 2018, documenting gender disparities that disfavour female litigants. We investigate the impact of an open justice reform that mandated courts to broadcast legal proceedings live on a centralized online platform. By exploiting variations in its implementation across courts and over time and employing both difference-in-differences and Bartik IV approaches, we find that gender disparities in chances of winning decrease as broadcast intensity increases. Analysis of the textual content of judicial decisions provides further evidence that these changes in judicial outcomes stem from altered judge behaviours ( i.e. attention and effort) under enhanced judicial transparency. Our results demonstrate how information technology shapes judges’ conduct, underscoring its broader potential to improve accountability in public institutions.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf039</t>
+          <t>10.1093/restud/rdaf066</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -4414,44 +4302,48 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cascades and Fluctuations in an Economy with an Endogenous Production Network</t>
+          <t>Reallocative Auctions and Core Selection</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thu, 22 May 2025 00:00:00 GMT</t>
+          <t>Thu, 31 Jul 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mathieu Taschereau-Dumouchel</t>
+          <t>Marzena Rostek; Nathan Yoder</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/1354/8140637?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/2058/8219939?rss=1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Abstract This article studies the efficient allocation in an economy in which firms are connected through input–output linkages and must pay a fixed cost to produce. When economic conditions are poor, some firms might decide not to operate, thereby severing the links with their neighbours and changing the structure of the production network. Since producers benefit from having access to additional suppliers, nearby firms tend to operate, or not, together. As a result, the production network features clusters of operating firms, and the exit of a producer can create a cascade of firm shutdowns. While well-connected firms are better able to withstand shocks, they trigger larger cascades upon exit. The theory also predicts how the structure of the production network changes over the business cycle. As in the data, recessions are associated with more dispersed networks that feature fewer highly connected firms. In the calibrated economy, the endogenous reorganization of the network substantially dampens the impact of idiosyncratic shocks on aggregate fluctuations.</t>
+          <t>Abstract When selling goods like wireless spectrum or electricity contracts, designers often opt for core-selecting mechanisms— i.e. those that induce outcomes in the core—in order to balance revenue and efficiency goals. But increasingly, auctions—such as the Federal Communications Commission’s Incentive Auction and those explored for natural resources—seek to reallocate goods, not just sell them. We show that when bidders can both buy and sell, substitutability among goods is no longer sufficient or necessary for core selection. In particular, in these environments, core selection can fail even with a single good and positive revenue, and can succeed even when some or all bidders view goods as complements. Instead, we show that the key feature that determines core selection is heterogeneity among the bidders. With too much heterogeneity, reallocation mostly realises pre-existing gains from trade among the bidders, and core selection fails. With limited heterogeneity, most gains from trade among the bidders are created by the quantity auctioned, and a core-selecting mechanism is possible.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf036</t>
+          <t>10.1093/restud/rdaf065</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>review</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>no priority JEL or keyword signal</t>
+          <t>weak keyword signal only: trade</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4468,32 +4360,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Racial Discrimination and the Social Contract: Evidence from U.S. Army Enlistment During WWII</t>
+          <t>Estimating Welfare Effects in a Non-Parametric Choice Model: The Case of School Vouchers</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Thu, 22 May 2025 00:00:00 GMT</t>
+          <t>Thu, 31 Jul 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Nancy Qian; Marco Tabellini</t>
+          <t>Vishal Kamat; Samuel Norris</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/1261/8140634?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1963/8219920?rss=1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Abstract This paper documents that the Pearl Harbor attack triggered a sharp increase in volunteer enlistment rates of American men, the magnitude of the increase was smaller for Black men than for White men and the Black–White gap was larger in counties with higher levels of racial discrimination. The results suggest that political exclusion and discrimination can undermine support for the government during critical times such as war.</t>
+          <t>Abstract We develop new robust discrete choice tools to learn about the average willingness to pay for a price subsidy and its effects on demand given exogenous, discrete variation in prices. Our starting point is a non-parametric, non-separable model of choice. We exploit the insight that our welfare parameters in this model can be expressed as functions of demand for the different alternatives. However, while the variation in the data reveals the value of demand at the observed prices, the parameters generally depend on its values beyond these prices. We show how to sharply characterize what we can learn when demand is specified to be entirely non-parametric or to be parametrized in a flexible manner, both of which imply that the parameters are not necessarily point identified. We use our tools to analyse the welfare effects of price subsidies provided by school vouchers in the DC Opportunity Scholarship Program. We find that the provision of the status quo voucher and a wide range of counterfactual vouchers of different amounts can have positive and potentially large benefits net of costs. The positive effect can be explained by the popularity of low-tuition schools in the programme; removing them from the programme can result in a negative net benefit. We also find that various standard logit specifications, in comparison, limit attention to demand functions with low demand for the voucher, which do not capture the large magnitudes of benefits credibly consistent with the data.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf038</t>
+          <t>10.1093/restud/rdaf064</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -4522,32 +4414,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Extreme Categories and Overreaction to News</t>
+          <t>Does Tax-Benefit Linkage Matter for the Incidence of Payroll Taxes?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thu, 22 May 2025 00:00:00 GMT</t>
+          <t>Wed, 23 Jul 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Spencer Y Kwon; Johnny Tang</t>
+          <t>Antoine Bozio; Thomas Breda; Julien Grenet; Arthur Guillouzouic</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/restud/article/93/2/1137/8140579?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1536/8210843?rss=1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Abstract What characteristics of news generate over-or-underreaction? We study the asset-pricing consequences of diagnostic expectations, a model of belief formation based on the representativeness heuristic, in a setting where news events are drawn from categories with extreme distributions of fundamentals. Our model predicts greater overreaction to news belonging to categories with more extreme outliers, or tail events. We test our theory on a comprehensive database of corporate news that includes news from twenty-four different categories, including earnings announcements, product launches, mergers and acquisition, business expansions, and client-related news. We find theory-consistent heterogeneity in investor reaction to news, with more overreaction in the form of greater post-announcement return reversals and trading volume for news categories with more extreme distributions of fundamentals.</t>
+          <t>Abstract We analyse earnings responses to six large payroll tax and income tax reforms in France. Our findings indicate full pass-through to workers when there is a strong and transparent link between contributions and expected benefits. In contrast, employer payroll taxes with no tax-benefit linkage exhibit limited pass-through to workers, while income tax nominally borne by employees show nearly full pass-through. Together with a meta-analysis of the literature, we interpret these results as empirical support for the long-standing hypothesis that tax-benefit linkage matters for the incidence of payroll taxes. In the absence of such linkage, our findings suggest that the individual-level incidence of payroll taxes aligns with their statutory incidence.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>10.1093/restud/rdaf037</t>
+          <t>10.1093/restud/rdaf059</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -4571,37 +4463,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>The Quarterly Journal of Economics</t>
+          <t>Review of Economic Studies</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Complete Pass-Through in Levels*</t>
+          <t>Capital Requirements with Non-Bank Finance*</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 00:00:00 GMT</t>
+          <t>Mon, 21 Jul 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Kunal Sangani</t>
+          <t>Kyle Dempsey</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/1077/8497409?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1635/8209607?rss=1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Abstract Empirical studies find that the pass-through of input cost changes to prices is incomplete: a 10% increase in costs causes downstream prices to rise less than 10%, even at long horizons. Using microdata from gas stations, food products, and manufacturing industries, I find that incomplete pass-through in percentages often disguises complete pass-through in levels : a $1/unit increase in input costs leads to $1/unit higher downstream prices. Pass-through appears incomplete in percentages due to a gap between prices and costs. Complete pass-through in levels contrasts with workhorse macroeconomic models that feature homothetic industry demand systems. I identify an alternative class of demand systems that yields pass-through in levels and highlight four implications. First, measuring pass-through in percentages can lead to spurious evidence of asymmetry and size dependence. Second, pass-through in levels leads to systematic fluctuations in relative price and markup dispersion that are not associated with changes in allocative efficiency. Third, pass-through in levels can explain dynamics of industry gross margins, operating profits, and entry in the data that are at odds with workhorse models. Finally, incorporating pass-through in levels into an input-output model of the U.S. economy better matches the volatility of consumer price inflation and the response of inflation to identified shocks.</t>
+          <t>Abstract I quantitatively analyse the macroeconomic impacts of raising capital requirements in a model in which heterogeneous firms may choose either intermediated or direct finance. Heterogeneous banks compete with other banks and the bond market, fund loans with insured deposits and costly equity (subject to a minimum capital-to-asset ratio), and monitor borrowers. I find that tighter capital requirements reduce costly bank failures while having only small effects on key macroeconomic aggregates, and that raising capital requirements above current levels can be welfare-improving. Three main forces give rise to these results. First, even though banks cut loan supply for a given level of net worth under a tighter capital requirement, in equilibrium banks’ net worth rises to dampen this effect. Second, intense competition from the non-bank sector disciplines banks’ lending responses to tighter regulation. Third, substitution by corporate firms offsets much of the decline in debt financing associated with tighter bank loan supply. As a corollary, almost all of the modest costs associated with tighter capital requirements are concentrated within the bank-dependent non-corporate sector.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjag014</t>
+          <t>10.1093/restud/rdaf061</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -4625,53 +4517,49 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>The Quarterly Journal of Economics</t>
+          <t>Review of Economic Studies</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Macroeconomic Impact of Climate Change: Global Versus Local Temperature*</t>
+          <t>Counterfactual Identification and Latent Space Enumeration in Discrete Outcome Models</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 00:00:00 GMT</t>
+          <t>Thu, 17 Jul 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Adrien Bilal; Diego R Känzig</t>
+          <t>Jiaying Gu; Thomas M Russell; Thomas Stringham</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/889/8490467?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1847/8205507?rss=1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Abstract This article estimates that the macroeconomic damages from climate change are an order of magnitude larger than previously thought. Exploiting natural global temperature variability, we find that 1ºC warming reduces world GDP by over 20% in the long run. Global temperature correlates strongly with extreme climatic events, unlike country-level temperature used in previous work, explaining our larger estimate. We use this evidence to estimate damage functions in a neoclassical growth model. Business-as-usual warming implies a present welfare loss of more than 30%, and a social cost of carbon in excess of $1,200 per ton. These impacts suggest that unilateral decarbonization policy is cost-effective for large countries such as the United States.</t>
+          <t>Abstract This article provides a unified framework for studying the identification of counterfactual parameters in a general class of discrete outcome models, allowing for endogenous regressors and multidimensional latent variables, all without parametric distributional assumptions. Our main theoretical result is that, when the covariates are discrete, the infinite-dimensional latent variable distribution can be replaced with a finite-dimensional version that is equivalent from an identification perspective. The finite-dimensional latent variable distribution is constructed in practice by enumerating regions of the latent variable space with a new and efficient cell enumeration algorithm for hyperplane arrangements. We then show that bounds on a certain class of counterfactual parameters can be computed by solving a sequence of linear programming problems, and show how the researcher can introduce additional assumptions as constraints in the linear programmes. Finally, we apply the method to a mobile phone choice example with heterogeneous choice sets, and to an airline entry game example.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjag011</t>
+          <t>10.1093/restud/rdaf058</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>climate; policy</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>weak keyword signal only: climate, policy</t>
+          <t>no priority JEL or keyword signal</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4683,49 +4571,53 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>The Quarterly Journal of Economics</t>
+          <t>Review of Economic Studies</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Civil War–Induced Displacement and Human Capital*</t>
+          <t>The Micro and Macro Effects of Changes in the Potential Benefit Duration</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 00:00:00 GMT</t>
+          <t>Thu, 17 Jul 2025 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Giorgio Chiovelli; Stelios Michalopoulos; Elias Papaioannou; Sandra Sequeira</t>
+          <t>Jonas Jessen; Robin Jessen; Ewa Gałecka-Burdziak; Marek Góra; Jochen Kluve</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/1211/8475342?rss=1</t>
+          <t>https://academic.oup.com/restud/article/93/3/1926/8205502?rss=1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Abstract We study the effect of conflict-induced displacement on human capital and occupational shifts, focusing on the Mozambican civil war (1977–1992), during which millions of civilians were forced to flee to the countryside, cities, and neighboring countries. Reconstructing the wartime mobility histories of the surviving population, we examine the consequences of multiple displacement trajectories in a unified framework. First, we characterize the education and sectoral employment of the universe of (non-)displaced. Second, we exploit differences in relocation trajectories among extended kin members during their schooling years. Displacement is associated with significant gains in education. Third, using a movers design, we show that minors displaced earlier to better districts experienced an increase in educational attainment. Focusing on moves during the intensification of the war and when comparing members of the same household, regional childhood exposure effects remain strong, whereas spatial sorting becomes negligible. Fourth, we jointly estimate place-based, spatial sorting, and uprootedness effects, showing that all forces are at play. Fifth, a small survey in Mozambique’s largest northern city reveals long-term effects: internally displaced people report higher education than their siblings who stayed behind but lower social capital and worse mental health relative to locals. Our findings demonstrate that displacement shocks can foster human capital accumulation, even in very low-income settings, albeit at the cost of enduring social and psychological traumas.</t>
+          <t>Abstract We quantify micro and macro effects of changes in the potential benefit duration (PBD) in unemployment insurance. In Poland, the PBD is 12 months for the newly unemployed if the previous year’s county unemployment rate is more than 150% of the national average, and 6 months otherwise. We exploit this cut-off using regression discontinuity estimates on registry data containing the universe of unemployed from 2005 to 2019. For those whose PBD is directly affected by the policy rule, benefit recipients younger than 50, a PBD increase from 6 to 12 months leads to 13% higher unemployment. A decomposition analysis reveals that 12 months after an increase in the PBD, only half of the increase in unemployment is due to the effect on search effort (the micro effect) while the other half is due to increased inflows into unemployment. The total effect on unemployment, which includes equilibrium effects, is entirely explained by the increase in unemployment of workers directly affected by the policy change. We find no evidence of spill-overs on two distinct groups of unemployed whose PBD is unchanged and no effect on measures of labour market tightness.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjag009</t>
+          <t>10.1093/restud/rdaf056</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>review</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>no priority JEL or keyword signal</t>
+          <t>weak keyword signal only: policy</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4742,48 +4634,44 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Disaggregated Economic Accounts*</t>
+          <t>Complete Pass-Through in Levels*</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 00:00:00 GMT</t>
+          <t>Wed, 25 Feb 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Asger Lau Andersen; Kilian Huber; Niels Johannesen; Ludwig Straub; Emil Toft Vestergaard</t>
+          <t>Kunal Sangani</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/1005/8472869?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/1077/8497409?rss=1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Abstract We develop a system of disaggregated economic accounts. The system breaks down national accounting positions into bilateral flows between consistently defined groups of consumers (consumer cells), groups of producers (producer cells), the government, and the rest of the world. We disaggregate the full circular flow of money, including consumer spending, labor compensation, firm profits, intermediates trade, foreign trade, and government transactions, while satisfying all national accounting identities. We implement the disaggregated system for small region-by-industry cells in Denmark and present stylized facts, such as variation in domestic spending, local and urban bias in consumer spending, and a pattern of triangular flows across regions. Cell-level measures of spending intensity capture how much spending by a cell contributes to the income of cells experiencing unemployment after a shock. Using a general equilibrium model, we show that fiscal transfers raise aggregate GDP by more when they target cells with high spending intensity on unemployed cells. The disaggregated economic accounts help governments select more effective policies.</t>
+          <t>Abstract Empirical studies find that the pass-through of input cost changes to prices is incomplete: a 10% increase in costs causes downstream prices to rise less than 10%, even at long horizons. Using microdata from gas stations, food products, and manufacturing industries, I find that incomplete pass-through in percentages often disguises complete pass-through in levels : a $1/unit increase in input costs leads to $1/unit higher downstream prices. Pass-through appears incomplete in percentages due to a gap between prices and costs. Complete pass-through in levels contrasts with workhorse macroeconomic models that feature homothetic industry demand systems. I identify an alternative class of demand systems that yields pass-through in levels and highlight four implications. First, measuring pass-through in percentages can lead to spurious evidence of asymmetry and size dependence. Second, pass-through in levels leads to systematic fluctuations in relative price and markup dispersion that are not associated with changes in allocative efficiency. Third, pass-through in levels can explain dynamics of industry gross margins, operating profits, and entry in the data that are at odds with workhorse models. Finally, incorporating pass-through in levels into an input-output model of the U.S. economy better matches the volatility of consumer price inflation and the response of inflation to identified shocks.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjag010</t>
+          <t>10.1093/qje/qjag014</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>trade</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>weak keyword signal only: trade</t>
+          <t>no priority JEL or keyword signal</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4800,44 +4688,48 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Insuring Peace: Index-Based Livestock Insurance, Droughts, and Conflict*</t>
+          <t>The Macroeconomic Impact of Climate Change: Global Versus Local Temperature*</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 00:00:00 GMT</t>
+          <t>Thu, 19 Feb 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Kai Gehring; Paul Schaudt</t>
+          <t>Adrien Bilal; Diego R Känzig</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/1269/8454927?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/889/8490467?rss=1</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Abstract We provide quasi-experimental evidence of how an innovative market-based solution using remote-sensing technology can mitigate drought-induced conflict. Droughts are a major driver of conflict in Africa, particularly between transhumant pastoralists and sedentary farmers. Index-Based Livestock Insurance (IBLI), a program piloted in Kenya, provides automated, preemptive payouts to pastoralists affected by droughts. Combining variation in rainfall and the staggered rollout of IBLI in Kenya over 2000–2020, we find that IBLI strongly reduces drought-induced conflict. Key mechanisms include a reduction in herd sizes, as well as income smoothing and asset price stabilization, contributing to an overall reduced migratory pressure for pastoralists. Our study suggests that market-based solutions are a scalable, cost-effective pathway to mitigate conflict, complementing political solutions such as power-sharing agreements and institutional reforms.</t>
+          <t>Abstract This article estimates that the macroeconomic damages from climate change are an order of magnitude larger than previously thought. Exploiting natural global temperature variability, we find that 1ºC warming reduces world GDP by over 20% in the long run. Global temperature correlates strongly with extreme climatic events, unlike country-level temperature used in previous work, explaining our larger estimate. We use this evidence to estimate damage functions in a neoclassical growth model. Business-as-usual warming implies a present welfare loss of more than 30%, and a social cost of carbon in excess of $1,200 per ton. These impacts suggest that unilateral decarbonization policy is cost-effective for large countries such as the United States.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjag005</t>
+          <t>10.1093/qje/qjag011</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>climate; policy</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>review</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>no priority JEL or keyword signal</t>
+          <t>weak keyword signal only: climate, policy</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4854,48 +4746,44 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A Theory of How Workers Keep up with Inflation*</t>
+          <t>Civil War–Induced Displacement and Human Capital*</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 00:00:00 GMT</t>
+          <t>Thu, 12 Feb 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Hassan Afrouzi; Andres Blanco; Andres Drenik; Erik Hurst</t>
+          <t>Giorgio Chiovelli; Stelios Michalopoulos; Elias Papaioannou; Sandra Sequeira</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/945/8445540?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/1211/8475342?rss=1</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Abstract We develop a model that integrates modern theories of labor market flows with nominal wage rigidities to study the consequences of inflation on the labor market. Nominal wage stickiness incentivizes workers to engage in job-to-job transitions after an unexpected increase in the price level. Such dynamics lead to a rise in aggregate vacancies associating a seemingly tight labor market with lower real wages—two facts observed during the recent inflation period. The calibrated model jointly matches aggregate and cross-sectional trends in worker flows and wages during the 2021–2024 period. Using historical data, we show that prior periods of high inflation were also associated with increasing vacancies and upward shifts in the Beveridge curve. Our results suggest that policy makers and academics should be cautious about viewing the rise in the vacancy-to-unemployment rate as a sign of a tight labor market during inflationary periods without holistically looking at other labor market indicators.</t>
+          <t>Abstract We study the effect of conflict-induced displacement on human capital and occupational shifts, focusing on the Mozambican civil war (1977–1992), during which millions of civilians were forced to flee to the countryside, cities, and neighboring countries. Reconstructing the wartime mobility histories of the surviving population, we examine the consequences of multiple displacement trajectories in a unified framework. First, we characterize the education and sectoral employment of the universe of (non-)displaced. Second, we exploit differences in relocation trajectories among extended kin members during their schooling years. Displacement is associated with significant gains in education. Third, using a movers design, we show that minors displaced earlier to better districts experienced an increase in educational attainment. Focusing on moves during the intensification of the war and when comparing members of the same household, regional childhood exposure effects remain strong, whereas spatial sorting becomes negligible. Fourth, we jointly estimate place-based, spatial sorting, and uprootedness effects, showing that all forces are at play. Fifth, a small survey in Mozambique’s largest northern city reveals long-term effects: internally displaced people report higher education than their siblings who stayed behind but lower social capital and worse mental health relative to locals. Our findings demonstrate that displacement shocks can foster human capital accumulation, even in very low-income settings, albeit at the cost of enduring social and psychological traumas.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjag007</t>
+          <t>10.1093/qje/qjag009</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>weak keyword signal only: policy</t>
+          <t>no priority JEL or keyword signal</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4912,40 +4800,48 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Acknowledgment of Referees</t>
+          <t>Disaggregated Economic Accounts*</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 00:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Wed, 11 Feb 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Asger Lau Andersen; Kilian Huber; Niels Johannesen; Ludwig Straub; Emil Toft Vestergaard</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/1823/8444573?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/1005/8472869?rss=1</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>The Quarterly Journal of Economics gratefully acknowledges the help of the people listed below who refereed four or more papers in 2025.</t>
+          <t>Abstract We develop a system of disaggregated economic accounts. The system breaks down national accounting positions into bilateral flows between consistently defined groups of consumers (consumer cells), groups of producers (producer cells), the government, and the rest of the world. We disaggregate the full circular flow of money, including consumer spending, labor compensation, firm profits, intermediates trade, foreign trade, and government transactions, while satisfying all national accounting identities. We implement the disaggregated system for small region-by-industry cells in Denmark and present stylized facts, such as variation in domestic spending, local and urban bias in consumer spending, and a pattern of triangular flows across regions. Cell-level measures of spending intensity capture how much spending by a cell contributes to the income of cells experiencing unemployment after a shock. Using a general equilibrium model, we show that fiscal transfers raise aggregate GDP by more when they target cells with high spending intensity on unemployed cells. The disaggregated economic accounts help governments select more effective policies.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjag008</t>
+          <t>10.1093/qje/qjag010</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>review</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>no priority JEL or keyword signal</t>
+          <t>weak keyword signal only: trade</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4962,32 +4858,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>How Do You Identify a Good Manager?*</t>
+          <t>Insuring Peace: Index-Based Livestock Insurance, Droughts, and Conflict*</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 00:00:00 GMT</t>
+          <t>Mon, 02 Feb 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ben Weidmann; Joseph Vecci; Farah Said; Sonia Bhalotra; Achyuta Adhvaryu; Anant Nyshadham; Jorge Tamayo; David Deming</t>
+          <t>Kai Gehring; Paul Schaudt</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/1581/8435315?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/1269/8454927?rss=1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Abstract We introduce and validate a novel approach to identifying good managers. In a preregistered lab experiment, we causally identify managerial contributions by randomly assigning managers to teams and controlling for individual skill. We find that manager contributions are crucial for team success, and that people who self-select into management roles perform worse than randomly assigned managers. Managerial performance is strongly predicted by economic decision-making skill but not by demographic characteristics. Two validation studies support our experimental results. Participants who succeed in the lab receive more real-world promotions and, in a separate study of retail store managers, skill measures strongly predict store sales. A one standard deviation increase in manager quality increases annual per store sales by US$4.1 million (25% increase). Selecting managers on skills rather than demographic characteristics or the desire to lead could substantially improve organizational performance.</t>
+          <t>Abstract We provide quasi-experimental evidence of how an innovative market-based solution using remote-sensing technology can mitigate drought-induced conflict. Droughts are a major driver of conflict in Africa, particularly between transhumant pastoralists and sedentary farmers. Index-Based Livestock Insurance (IBLI), a program piloted in Kenya, provides automated, preemptive payouts to pastoralists affected by droughts. Combining variation in rainfall and the staggered rollout of IBLI in Kenya over 2000–2020, we find that IBLI strongly reduces drought-induced conflict. Key mechanisms include a reduction in herd sizes, as well as income smoothing and asset price stabilization, contributing to an overall reduced migratory pressure for pastoralists. Our study suggests that market-based solutions are a scalable, cost-effective pathway to mitigate conflict, complementing political solutions such as power-sharing agreements and institutional reforms.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjag004</t>
+          <t>10.1093/qje/qjag005</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -5016,44 +4912,48 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>(Not) Thinking About the Future: Financial Information and Maternal Labor Supply*</t>
+          <t>A Theory of How Workers Keep up with Inflation*</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 00:00:00 GMT</t>
+          <t>Fri, 30 Jan 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ana Costa-Ramón; Michaela Slotwinski; Ursina Schaede; Anne Ardila Brenøe</t>
+          <t>Hassan Afrouzi; Andres Blanco; Andres Drenik; Erik Hurst</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/1335/8431411?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/945/8445540?rss=1</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Abstract Does information about the long-run financial costs of reduced labor supply increase mothers’ working hours? We document descriptively that long-term financial factors are not top of mind when mothers decide on their employment level. Moreover, a substantial share of women holds overly optimistic expectations about pension receipt and wage growth under part-time work. In a large-scale field experiment in Switzerland, we randomly assign mothers working part-time as teachers to receive objective information about the long-run costs of reduced labor supply. The treatment increases both demand for financial information and future labor supply plans, in particular among women who underestimate the costs of part-time work. Leveraging linked employer administrative data one year post-intervention, we find that this group of mothers increases working hours by 7%. These findings underscore that policies reducing information frictions in labor supply decisions may help address remaining gender gaps in the labor market.</t>
+          <t>Abstract We develop a model that integrates modern theories of labor market flows with nominal wage rigidities to study the consequences of inflation on the labor market. Nominal wage stickiness incentivizes workers to engage in job-to-job transitions after an unexpected increase in the price level. Such dynamics lead to a rise in aggregate vacancies associating a seemingly tight labor market with lower real wages—two facts observed during the recent inflation period. The calibrated model jointly matches aggregate and cross-sectional trends in worker flows and wages during the 2021–2024 period. Using historical data, we show that prior periods of high inflation were also associated with increasing vacancies and upward shifts in the Beveridge curve. Our results suggest that policy makers and academics should be cautious about viewing the rise in the vacancy-to-unemployment rate as a sign of a tight labor market during inflationary periods without holistically looking at other labor market indicators.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjag003</t>
+          <t>10.1093/qje/qjag007</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>review</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>no priority JEL or keyword signal</t>
+          <t>weak keyword signal only: policy</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5070,32 +4970,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Future in Mind: Aspirations and Long-Term Outcomes in Rural Ethiopia*</t>
+          <t>Acknowledgment of Referees</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 00:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Tanguy Bernard; Stefan Dercon; Kate Orkin; Giulio Schinaia; Alemayehu Seyoum Taffesse</t>
-        </is>
-      </c>
+          <t>Thu, 29 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/1383/8429789?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/1823/8444573?rss=1</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Abstract Aspirations may condition the future-oriented choices of individuals and thus may play a role in the persistence of poverty or the effort to break out of it. We run a randomized controlled trial in remote, rural Ethiopia to explore this and evaluate an intervention that aims to change how poor people perceive their future opportunities, alter their aspirations, and through that, modify their investment decisions. A treatment group was shown video documentaries featuring individuals from similar communities who escaped poverty through their own efforts and who serve as relatable role models. Five years after the screening took place, the treated households had increased future-oriented investments in agriculture, children’s education, and assets. The results can be explained by an increase in aspirations in terms of lifetime goals. Overall, this research uniquely provides evidence that a light-touch behavioural intervention can have persistent economic impacts on a poor population.</t>
+          <t>The Quarterly Journal of Economics gratefully acknowledges the help of the people listed below who refereed four or more papers in 2025.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjag002</t>
+          <t>10.1093/qje/qjag008</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -5124,48 +5020,44 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Leveraging Virtual Contact and Social Networks to Foster Interethnic Harmony*</t>
+          <t>How Do You Identify a Good Manager?*</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 00:00:00 GMT</t>
+          <t>Wed, 21 Jan 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Abu Siddique; Michael Vlassopoulos; Yves Zenou</t>
+          <t>Ben Weidmann; Joseph Vecci; Farah Said; Sonia Bhalotra; Achyuta Adhvaryu; Anant Nyshadham; Jorge Tamayo; David Deming</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/1449/8426299?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/1581/8435315?rss=1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Abstract This article investigates whether virtual contact, initiated through a documentary film, can promote interethnic harmony. We carried out a cluster-randomized field experiment involving over 3,300 households across 121 multiethnic villages in Bangladesh. We find that a documentary film, designed to humanize the ethnic-minority Santals and evoke empathy among the ethnic majority Bengalis, increased the ethnic majority’s prosociality toward minorities, though the strength of the evidence varies by treatment arm and outcome. Using emotion-detecting software to analyze facial expressions during the film viewing suggests that the documentary elicited emotional responses consistent with empathy. We do not find evidence that the intervention reduced the prevalence of negative stereotypes and discriminatory opinions toward minorities. In villages assigned to target network-central people, we find positive behavioral effects on untreated individuals, including Santals, and village-level administrative data suggest a reduction in police complaints in those villages. About five months after the intervention, we conducted a casual-work field experiment involving 720 participants from the main intervention. In this task, pairs of ethnic-majority and minority participants jointly produced paper bags for a local supplier under a piece-rate compensation scheme. We find positive treatment effects on productivity for both ethnic groups, with effects concentrated in villages where network-central people were treated. For the ethnic majority, increased prosociality, and for the ethnic minority, reciprocity or peer pressure may have contributed to increased productivity. Overall, our findings suggest that virtual contact and social networks may help promote harmony in multiethnic communities.</t>
+          <t>Abstract We introduce and validate a novel approach to identifying good managers. In a preregistered lab experiment, we causally identify managerial contributions by randomly assigning managers to teams and controlling for individual skill. We find that manager contributions are crucial for team success, and that people who self-select into management roles perform worse than randomly assigned managers. Managerial performance is strongly predicted by economic decision-making skill but not by demographic characteristics. Two validation studies support our experimental results. Participants who succeed in the lab receive more real-world promotions and, in a separate study of retail store managers, skill measures strongly predict store sales. A one standard deviation increase in manager quality increases annual per store sales by US$4.1 million (25% increase). Selecting managers on skills rather than demographic characteristics or the desire to lead could substantially improve organizational performance.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjag001</t>
+          <t>10.1093/qje/qjag004</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>productivity</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>weak keyword signal only: productivity</t>
+          <t>no priority JEL or keyword signal</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5182,32 +5074,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Growth Experiences and Trust in Government*</t>
+          <t>(Not) Thinking About the Future: Financial Information and Maternal Labor Supply*</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 00:00:00 GMT</t>
+          <t>Tue, 20 Jan 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Timothy Besley; Christopher Dann; Sacha Dray</t>
+          <t>Ana Costa-Ramón; Michaela Slotwinski; Ursina Schaede; Anne Ardila Brenøe</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/1761/8424246?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/1335/8431411?rss=1</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Abstract This article explores the relationship between economic growth and trust in government using variation in GDP growth experienced over a lifetime since birth. We assemble a newly harmonized global data set across 11 major opinion surveys, comprising 3.3 million respondents in 166 countries since 1990. Exploiting cohort-level variation, we find that people who have experienced higher GDP growth are more prone to trust their governments, with larger effects found in democracies. Higher-growth experiences are also associated with improved perceptions of government performance and living standards. We find no similar channel between growth experience and interpersonal trust. Second, more recent growth experiences appear to matter most for trust in government, with no detectable effect of growth experienced during one’s formative years, closer to birth, or before birth. Third, we find evidence of a “trust paradox” whereby average trust in government is lower in democracies than in autocracies. Our results are robust to a range of falsification exercises, robustness checks, and single-country evidence using the American National Election Studies and the Swiss Household Panel.</t>
+          <t>Abstract Does information about the long-run financial costs of reduced labor supply increase mothers’ working hours? We document descriptively that long-term financial factors are not top of mind when mothers decide on their employment level. Moreover, a substantial share of women holds overly optimistic expectations about pension receipt and wage growth under part-time work. In a large-scale field experiment in Switzerland, we randomly assign mothers working part-time as teachers to receive objective information about the long-run costs of reduced labor supply. The treatment increases both demand for financial information and future labor supply plans, in particular among women who underestimate the costs of part-time work. Leveraging linked employer administrative data one year post-intervention, we find that this group of mothers increases working hours by 7%. These findings underscore that policies reducing information frictions in labor supply decisions may help address remaining gender gaps in the labor market.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjaf056</t>
+          <t>10.1093/qje/qjag003</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -5236,32 +5128,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Changing Opportunity: Sociological Mechanisms Underlying Growing Class Gaps and Shrinking Race Gaps in Economic Mobility*</t>
+          <t>The Future in Mind: Aspirations and Long-Term Outcomes in Rural Ethiopia*</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Thu, 08 Jan 2026 00:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Raj Chetty; Will Dobbie; Benjamin Goldman; Sonya R Porter; Crystal S Yang</t>
+          <t>Tanguy Bernard; Stefan Dercon; Kate Orkin; Giulio Schinaia; Alemayehu Seyoum Taffesse</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/qje/article/141/2/1137/8417176?rss=1</t>
+          <t>https://academic.oup.com/qje/article/141/2/1383/8429789?rss=1</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Abstract We show that intergenerational mobility changed rapidly by race and class in recent decades in the United States and study the causal mechanisms underlying those changes. Between the 1978 and 1992 birth cohorts, earnings increased for white children from high-income families relative to white children from low-income families, increasing earnings gaps by parental income (class) by 30%. Earnings increased for Black children at all parental income levels, reducing white-Black earnings gaps for children from low-income families by 30%. Class gaps grew and race gaps shrank similarly for nonmonetary outcomes such as educational attainment, standardized test scores, and mortality rates. Using a quasi-experimental design, we show that the divergent trends in economic mobility were caused by differential changes in childhood environments, as proxied by parental employment rates, in local communities defined by race, class, and childhood county. Outcomes improve across birth cohorts for children who grow up in communities with increasing parental employment rates, with larger effects for children who move to such communities at younger ages. Children’s outcomes are most strongly related to the parental employment rates of peers they are more likely to interact with, such as those in their own birth cohort, suggesting that the relationship between children’s outcomes and parental employment rates is mediated by social interaction.</t>
+          <t>Abstract Aspirations may condition the future-oriented choices of individuals and thus may play a role in the persistence of poverty or the effort to break out of it. We run a randomized controlled trial in remote, rural Ethiopia to explore this and evaluate an intervention that aims to change how poor people perceive their future opportunities, alter their aspirations, and through that, modify their investment decisions. A treatment group was shown video documentaries featuring individuals from similar communities who escaped poverty through their own efforts and who serve as relatable role models. Five years after the screening took place, the treated households had increased future-oriented investments in agriculture, children’s education, and assets. The results can be explained by an increase in aspirations in terms of lifetime goals. Overall, this research uniquely provides evidence that a light-touch behavioural intervention can have persistent economic impacts on a poor population.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>10.1093/qje/qjaf057</t>
+          <t>10.1093/qje/qjag002</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -5277,6 +5169,172 @@
         </is>
       </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t>rss+crossref</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>The Quarterly Journal of Economics</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Leveraging Virtual Contact and Social Networks to Foster Interethnic Harmony*</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Abu Siddique; Michael Vlassopoulos; Yves Zenou</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://academic.oup.com/qje/article/141/2/1449/8426299?rss=1</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Abstract This article investigates whether virtual contact, initiated through a documentary film, can promote interethnic harmony. We carried out a cluster-randomized field experiment involving over 3,300 households across 121 multiethnic villages in Bangladesh. We find that a documentary film, designed to humanize the ethnic-minority Santals and evoke empathy among the ethnic majority Bengalis, increased the ethnic majority’s prosociality toward minorities, though the strength of the evidence varies by treatment arm and outcome. Using emotion-detecting software to analyze facial expressions during the film viewing suggests that the documentary elicited emotional responses consistent with empathy. We do not find evidence that the intervention reduced the prevalence of negative stereotypes and discriminatory opinions toward minorities. In villages assigned to target network-central people, we find positive behavioral effects on untreated individuals, including Santals, and village-level administrative data suggest a reduction in police complaints in those villages. About five months after the intervention, we conducted a casual-work field experiment involving 720 participants from the main intervention. In this task, pairs of ethnic-majority and minority participants jointly produced paper bags for a local supplier under a piece-rate compensation scheme. We find positive treatment effects on productivity for both ethnic groups, with effects concentrated in villages where network-central people were treated. For the ethnic majority, increased prosociality, and for the ethnic minority, reciprocity or peer pressure may have contributed to increased productivity. Overall, our findings suggest that virtual contact and social networks may help promote harmony in multiethnic communities.</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>10.1093/qje/qjag001</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>weak keyword signal only: productivity</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>rss+crossref</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>The Quarterly Journal of Economics</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Growth Experiences and Trust in Government*</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Timothy Besley; Christopher Dann; Sacha Dray</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://academic.oup.com/qje/article/141/2/1761/8424246?rss=1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Abstract This article explores the relationship between economic growth and trust in government using variation in GDP growth experienced over a lifetime since birth. We assemble a newly harmonized global data set across 11 major opinion surveys, comprising 3.3 million respondents in 166 countries since 1990. Exploiting cohort-level variation, we find that people who have experienced higher GDP growth are more prone to trust their governments, with larger effects found in democracies. Higher-growth experiences are also associated with improved perceptions of government performance and living standards. We find no similar channel between growth experience and interpersonal trust. Second, more recent growth experiences appear to matter most for trust in government, with no detectable effect of growth experienced during one’s formative years, closer to birth, or before birth. Third, we find evidence of a “trust paradox” whereby average trust in government is lower in democracies than in autocracies. Our results are robust to a range of falsification exercises, robustness checks, and single-country evidence using the American National Election Studies and the Swiss Household Panel.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>10.1093/qje/qjaf056</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>no priority JEL or keyword signal</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>rss+crossref</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>The Quarterly Journal of Economics</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Changing Opportunity: Sociological Mechanisms Underlying Growing Class Gaps and Shrinking Race Gaps in Economic Mobility*</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Thu, 08 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Raj Chetty; Will Dobbie; Benjamin Goldman; Sonya R Porter; Crystal S Yang</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://academic.oup.com/qje/article/141/2/1137/8417176?rss=1</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Abstract We show that intergenerational mobility changed rapidly by race and class in recent decades in the United States and study the causal mechanisms underlying those changes. Between the 1978 and 1992 birth cohorts, earnings increased for white children from high-income families relative to white children from low-income families, increasing earnings gaps by parental income (class) by 30%. Earnings increased for Black children at all parental income levels, reducing white-Black earnings gaps for children from low-income families by 30%. Class gaps grew and race gaps shrank similarly for nonmonetary outcomes such as educational attainment, standardized test scores, and mortality rates. Using a quasi-experimental design, we show that the divergent trends in economic mobility were caused by differential changes in childhood environments, as proxied by parental employment rates, in local communities defined by race, class, and childhood county. Outcomes improve across birth cohorts for children who grow up in communities with increasing parental employment rates, with larger effects for children who move to such communities at younger ages. Children’s outcomes are most strongly related to the parental employment rates of peers they are more likely to interact with, such as those in their own birth cohort, suggesting that the relationship between children’s outcomes and parental employment rates is mediated by social interaction.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>10.1093/qje/qjaf057</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>no priority JEL or keyword signal</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t>rss+crossref</t>
         </is>
